--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2103-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2103-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D04C0CB9-F5BE-4E54-A39D-6EB23DE38053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8371662-9AC6-416A-9774-99A4DE2239B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{928138CF-C0B2-4115-A24A-86FE787ABA2F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{85C3DE3C-823B-4BFA-B6E1-325D93CE3A29}"/>
   </bookViews>
   <sheets>
     <sheet name="2103-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1508,29 +1508,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F55545-BCF8-4084-A5B4-EE47D206ADBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE329E8A-42F6-4A60-AB0F-298FB4491D7A}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1563,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1600,7 +1599,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1652,7 +1651,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1720,7 +1719,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1792,7 +1791,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2080,7 +2079,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2152,7 +2151,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2224,7 +2223,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2296,7 +2295,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2368,7 +2367,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2440,7 +2439,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2512,7 +2511,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2584,7 +2583,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2656,7 +2655,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2728,7 +2727,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2800,7 +2799,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2944,7 +2943,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -3016,7 +3015,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3088,7 +3087,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3160,7 +3159,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3232,7 +3231,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3304,7 +3303,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3376,7 +3375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2001</v>
       </c>
@@ -3448,7 +3447,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2000</v>
       </c>
@@ -3520,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1999</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>1998</v>
       </c>
@@ -3664,7 +3663,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1997</v>
       </c>
@@ -3736,7 +3735,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>1996</v>
       </c>
@@ -3808,7 +3807,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1995</v>
       </c>
@@ -3880,7 +3879,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>1994</v>
       </c>
@@ -3952,7 +3951,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1993</v>
       </c>
@@ -4024,7 +4023,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>1992</v>
       </c>
@@ -4096,7 +4095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1991</v>
       </c>
@@ -4168,7 +4167,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>1990</v>
       </c>
@@ -4240,7 +4239,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1989</v>
       </c>
@@ -4312,7 +4311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>1988</v>
       </c>
@@ -4384,7 +4383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1987</v>
       </c>
@@ -4456,7 +4455,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>1986</v>
       </c>
@@ -4528,7 +4527,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>1985</v>
       </c>
@@ -4600,7 +4599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>1984</v>
       </c>
@@ -4672,7 +4671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>1983</v>
       </c>
@@ -4744,7 +4743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
         <v>60</v>
       </c>
